--- a/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
+++ b/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_財務経営指標分析" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_R7決算サマリと差異" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_会計システム見直し" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_経営比較分析表_指標検証" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +144,24 @@
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
       <sz val="9"/>
     </font>
     <font>
@@ -364,33 +383,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -399,13 +418,13 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,6 +558,42 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9374,4 +9429,2444 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>総務省　経営比較分析表　指標の検証　－　令和７年度決算による再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>R1〜R5＝公表済の経営比較分析表（令和５年度決算）の値。R6・R7＝決算書および決算書掲載の経営指標から算定した値（決算統計提出前のため概算）。算式は公表値で検証済（R5の料金回収率52.87％・給水原価218.64円を再現）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>■　上水道事業（法適用・末端給水事業）　　類似団体区分 A8　／　R5 自己資本構成比率 91.91％・普及率 99.97％・1か月20㎥当たり家庭料金 2,470円</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>指　標</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C5" s="67" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D5" s="67" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F5" s="67" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="H5" s="67" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="I5" s="67" t="inlineStr">
+        <is>
+          <t>類似団体
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="J5" s="67" t="inlineStr">
+        <is>
+          <t>全国
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="K5" s="67" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="L5" s="67" t="inlineStr">
+        <is>
+          <t>コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="68" t="inlineStr">
+        <is>
+          <t>①経常収支比率（％）</t>
+        </is>
+      </c>
+      <c r="B6" s="69" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="C6" s="69" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="D6" s="69" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="E6" s="69" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="F6" s="69" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="G6" s="69" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="H6" s="69" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I6" s="69" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="J6" s="69" t="n">
+        <v>108.24</v>
+      </c>
+      <c r="K6" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L6" s="58" t="inlineStr">
+        <is>
+          <t>R7の改善は繰出基準外の他会計補助金166,434千円によるもの。これを除くと72.44％</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>②累積欠損金比率（％）</t>
+        </is>
+      </c>
+      <c r="B7" s="69" t="n">
+        <v>610.0700000000001</v>
+      </c>
+      <c r="C7" s="69" t="n">
+        <v>731.27</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>755.4299999999999</v>
+      </c>
+      <c r="E7" s="69" t="n">
+        <v>855.55</v>
+      </c>
+      <c r="F7" s="69" t="n">
+        <v>898.52</v>
+      </c>
+      <c r="G7" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H7" s="69" t="inlineStr">
+        <is>
+          <t>2,286.55</t>
+        </is>
+      </c>
+      <c r="I7" s="69" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="J7" s="69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L7" s="58" t="inlineStr">
+        <is>
+          <t>★過年度修正で欠損金27.3億円。類似団体平均の82倍。経営戦略（案）に記載なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="71" t="inlineStr">
+        <is>
+          <t>③流動比率（％）</t>
+        </is>
+      </c>
+      <c r="B8" s="72" t="n">
+        <v>105.92</v>
+      </c>
+      <c r="C8" s="72" t="n">
+        <v>142.15</v>
+      </c>
+      <c r="D8" s="72" t="n">
+        <v>160.94</v>
+      </c>
+      <c r="E8" s="72" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="F8" s="72" t="n">
+        <v>188.42</v>
+      </c>
+      <c r="G8" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H8" s="72" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="I8" s="72" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="J8" s="72" t="n">
+        <v>243.36</v>
+      </c>
+      <c r="K8" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L8" s="60" t="inlineStr">
+        <is>
+          <t>100％は上回るが低下。現金預金は1年で114,627千円減</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>④企業債残高対給水収益比率（％）</t>
+        </is>
+      </c>
+      <c r="B9" s="69" t="n">
+        <v>307.15</v>
+      </c>
+      <c r="C9" s="69" t="n">
+        <v>290.42</v>
+      </c>
+      <c r="D9" s="69" t="n">
+        <v>484.15</v>
+      </c>
+      <c r="E9" s="69" t="n">
+        <v>534.35</v>
+      </c>
+      <c r="F9" s="69" t="n">
+        <v>633.04</v>
+      </c>
+      <c r="G9" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H9" s="69" t="n">
+        <v>915.92</v>
+      </c>
+      <c r="I9" s="69" t="n">
+        <v>515.14</v>
+      </c>
+      <c r="J9" s="69" t="n">
+        <v>265.93</v>
+      </c>
+      <c r="K9" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L9" s="58" t="inlineStr">
+        <is>
+          <t>企業債残高1,094,346千円（決算書明細と一致）。R5から282.9pt悪化</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>⑤料金回収率（％）</t>
+        </is>
+      </c>
+      <c r="B10" s="69" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="C10" s="69" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E10" s="69" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="F10" s="69" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="G10" s="69" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="H10" s="69" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="I10" s="69" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="J10" s="69" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="K10" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L10" s="58" t="inlineStr">
+        <is>
+          <t>全国平均の約1/3。決算書掲載値と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>⑥給水原価（円）</t>
+        </is>
+      </c>
+      <c r="B11" s="69" t="n">
+        <v>223.79</v>
+      </c>
+      <c r="C11" s="69" t="n">
+        <v>200.23</v>
+      </c>
+      <c r="D11" s="69" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="E11" s="69" t="n">
+        <v>267.84</v>
+      </c>
+      <c r="F11" s="69" t="n">
+        <v>218.64</v>
+      </c>
+      <c r="G11" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H11" s="69" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="I11" s="69" t="n">
+        <v>230.21</v>
+      </c>
+      <c r="J11" s="69" t="n">
+        <v>177.56</v>
+      </c>
+      <c r="K11" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L11" s="58" t="inlineStr">
+        <is>
+          <t>R5から113.86円上昇。捨水・江島応急給水が主因。※意見書の658.74円は別算式</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>⑦施設利用率（％）</t>
+        </is>
+      </c>
+      <c r="B12" s="69" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="C12" s="69" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="E12" s="69" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F12" s="69" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="G12" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H12" s="69" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="I12" s="69" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="J12" s="69" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="K12" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L12" s="58" t="inlineStr">
+        <is>
+          <t>上昇は捨水による配水量増によるもので実質的改善ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t>⑧有収率（％）</t>
+        </is>
+      </c>
+      <c r="B13" s="69" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="C13" s="69" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E13" s="69" t="n">
+        <v>86.14</v>
+      </c>
+      <c r="F13" s="69" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="G13" s="69" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="H13" s="69" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="I13" s="69" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="J13" s="69" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="K13" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L13" s="58" t="inlineStr">
+        <is>
+          <t>★R5から13.84pt低下し、類似団体平均も下回った</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="74" t="inlineStr">
+        <is>
+          <t>2①有形固定資産減価償却率（％）</t>
+        </is>
+      </c>
+      <c r="B14" s="75" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="C14" s="75" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="D14" s="75" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="E14" s="75" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="F14" s="75" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G14" s="75" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="H14" s="75" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="I14" s="75" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="J14" s="75" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="K14" s="76" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L14" s="62" t="inlineStr">
+        <is>
+          <t>復旧復興で資産が新しい。ただし年約2.5ptずつ上昇</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="71" t="inlineStr">
+        <is>
+          <t>2②管路経年化率（％）</t>
+        </is>
+      </c>
+      <c r="B15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="72" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="H15" s="72" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="I15" s="72" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J15" s="72" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="K15" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L15" s="60" t="inlineStr">
+        <is>
+          <t>★公表値はR1〜R5すべて0だが決算書はR4・R5とも15.60％。公表値の要検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>2③管路更新率（％）</t>
+        </is>
+      </c>
+      <c r="B16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="72" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H16" s="72" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I16" s="72" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J16" s="72" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K16" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L16" s="60" t="inlineStr">
+        <is>
+          <t>★同上（決算書はR4・R5とも0.00％）。経年化率23.16％に対し更新ペースが不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>■　公共下水道事業（法適用）　　類似団体区分 Cd2（宮城県内 Cd1・Cd2 の10団体）　／　R5 自己資本構成比率 76.40％・普及率 87.47％・1か月20㎥当たり家庭料金 3,520円</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>指　標</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="H19" s="67" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="I19" s="67" t="inlineStr">
+        <is>
+          <t>類似団体
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="J19" s="67" t="inlineStr">
+        <is>
+          <t>全国
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="K19" s="67" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="L19" s="67" t="inlineStr">
+        <is>
+          <t>コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>①経常収支比率（％）</t>
+        </is>
+      </c>
+      <c r="B20" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D20" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E20" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>78.86</v>
+      </c>
+      <c r="G20" s="69" t="inlineStr">
+        <is>
+          <t>79.07</t>
+        </is>
+      </c>
+      <c r="H20" s="69" t="inlineStr">
+        <is>
+          <t>78.76</t>
+        </is>
+      </c>
+      <c r="I20" s="69" t="n">
+        <v>104.88</v>
+      </c>
+      <c r="J20" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K20" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="inlineStr">
+        <is>
+          <t>★決算書掲載の「経営収支比率」（R4:76.12／R5:78.69／R6:77.97／R7:69.96）は「経常収益÷総費用」で算式が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="68" t="inlineStr">
+        <is>
+          <t>②累積欠損金比率（％）</t>
+        </is>
+      </c>
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H21" s="69" t="inlineStr">
+        <is>
+          <t>287.95</t>
+        </is>
+      </c>
+      <c r="I21" s="69" t="n">
+        <v>53.26</v>
+      </c>
+      <c r="J21" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K21" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t>会計全体の欠損金540,833千円で試算。公共／浄化槽の按分は決算統計で確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>③流動比率（％）</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F22" s="69" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H22" s="69" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I22" s="69" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="J22" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K22" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t>会計全体。翌年度償還企業債195,448千円は全額一般会計負担見込（決算書注記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>④企業債残高対事業規模比率（％）</t>
+        </is>
+      </c>
+      <c r="B23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F23" s="72" t="inlineStr">
+        <is>
+          <t>1,734.22</t>
+        </is>
+      </c>
+      <c r="G23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H23" s="72" t="inlineStr">
+        <is>
+          <t>約1,540</t>
+        </is>
+      </c>
+      <c r="I23" s="72" t="inlineStr">
+        <is>
+          <t>1,200.63</t>
+        </is>
+      </c>
+      <c r="J23" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K23" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L23" s="60" t="inlineStr">
+        <is>
+          <t>企業債残高は減少中で改善方向。公共分の按分と分母の確定が必要（概算値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>⑤経費回収率（％）</t>
+        </is>
+      </c>
+      <c r="B24" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="E24" s="69" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="F24" s="69" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="G24" s="69" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="H24" s="69" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="I24" s="69" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="J24" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K24" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t>R5は公表値と決算書が一致。以後3年連続で低下。使用料単価189.99円</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="68" t="inlineStr">
+        <is>
+          <t>⑥汚水処理原価（円）</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F25" s="69" t="n">
+        <v>213.93</v>
+      </c>
+      <c r="G25" s="69" t="inlineStr">
+        <is>
+          <t>226.9</t>
+        </is>
+      </c>
+      <c r="H25" s="69" t="inlineStr">
+        <is>
+          <t>248.74</t>
+        </is>
+      </c>
+      <c r="I25" s="69" t="n">
+        <v>204.91</v>
+      </c>
+      <c r="J25" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K25" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr">
+        <is>
+          <t>使用料単価÷経費回収率で算定。R5から34.81円上昇。総務省の求める水準は150円</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>⑦施設利用率（％）</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="H26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="I26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J26" s="33" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K26" s="78" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="L26" s="34" t="inlineStr">
+        <is>
+          <t>終末処理場を有しないため算定対象外（流域下水道に接続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="74" t="inlineStr">
+        <is>
+          <t>⑧水洗化率（％）</t>
+        </is>
+      </c>
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C27" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D27" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F27" s="75" t="n">
+        <v>91.37</v>
+      </c>
+      <c r="G27" s="75" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="H27" s="75" t="inlineStr">
+        <is>
+          <t>約91</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="J27" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K27" s="76" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L27" s="62" t="inlineStr">
+        <is>
+          <t>類似団体平均を上回る。R7の水洗化人口は4,527人</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="74" t="inlineStr">
+        <is>
+          <t>2①有形固定資産減価償却率（％）</t>
+        </is>
+      </c>
+      <c r="B28" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C28" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D28" s="75" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E28" s="75" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F28" s="75" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="G28" s="75" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H28" s="75" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="I28" s="75" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="J28" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K28" s="76" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L28" s="62" t="inlineStr">
+        <is>
+          <t>決算書ベース。経営比較分析表のR5公表値は4.59％で、分母の取り方が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="74" t="inlineStr">
+        <is>
+          <t>2②管渠老朽化率（％）</t>
+        </is>
+      </c>
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C29" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J29" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K29" s="76" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L29" s="62" t="inlineStr">
+        <is>
+          <t>法定耐用年数未到達</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="71" t="inlineStr">
+        <is>
+          <t>2③管渠改善率（％）</t>
+        </is>
+      </c>
+      <c r="B30" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C30" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J30" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K30" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L30" s="60" t="inlineStr">
+        <is>
+          <t>R7から老朽管更新事業に着手。決算統計での計上要否を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t>■　浄化槽事業（法適用・下水道事業会計の報告セグメント）　　経営比較分析表の公表は決算統計での事業区分による。現状は決算書掲載の経営指標のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>指　標</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D33" s="67" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="H33" s="67" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="I33" s="67" t="inlineStr">
+        <is>
+          <t>類似団体
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="J33" s="67" t="inlineStr">
+        <is>
+          <t>全国
+平均(R5)</t>
+        </is>
+      </c>
+      <c r="K33" s="67" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="L33" s="67" t="inlineStr">
+        <is>
+          <t>コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="71" t="inlineStr">
+        <is>
+          <t>①経常収支比率（％）</t>
+        </is>
+      </c>
+      <c r="B34" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C34" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D34" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E34" s="72" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="F34" s="72" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="G34" s="72" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="H34" s="72" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="I34" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J34" s="72" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K34" s="73" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L34" s="60" t="inlineStr">
+        <is>
+          <t>ほぼ均衡。ただし他会計補助金4,813千円（収益の21.57％）に依存</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>⑤経費回収率（％）</t>
+        </is>
+      </c>
+      <c r="B35" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C35" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D35" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E35" s="69" t="n">
+        <v>65.41</v>
+      </c>
+      <c r="F35" s="69" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="G35" s="69" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="H35" s="69" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I35" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K35" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L35" s="58" t="inlineStr">
+        <is>
+          <t>★R6の74.48％から10.08pt急落。使用料水準の検証が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>⑥汚水処理原価（円）</t>
+        </is>
+      </c>
+      <c r="B36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F36" s="69" t="inlineStr">
+        <is>
+          <t>253.9</t>
+        </is>
+      </c>
+      <c r="G36" s="69" t="inlineStr">
+        <is>
+          <t>246.8</t>
+        </is>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>285.90</t>
+        </is>
+      </c>
+      <c r="I36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J36" s="69" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K36" s="70" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="L36" s="58" t="inlineStr">
+        <is>
+          <t>使用料単価（R7:184.12円）÷経費回収率で算定。R6から39.1円上昇</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="74" t="inlineStr">
+        <is>
+          <t>2①有形固定資産減価償却率（％）</t>
+        </is>
+      </c>
+      <c r="B37" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="C37" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D37" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="F37" s="75" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="G37" s="75" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="H37" s="75" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="I37" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="J37" s="75" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="K37" s="76" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L37" s="62" t="inlineStr">
+        <is>
+          <t>年約5ptずつ上昇。更新需要の把握が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="54" t="inlineStr">
+        <is>
+          <t>■　参考　－　繰出基準外の他会計補助金を除いた場合の上水道事業（実質値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="55" t="inlineStr">
+        <is>
+          <t>区　分</t>
+        </is>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>金　額（円）</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>内　容</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>経常収益（決算値）</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>655,339,107</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>うち他会計補助金 166,987,093円</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち繰出基準内</t>
+        </is>
+      </c>
+      <c r="B42" s="66" t="inlineStr">
+        <is>
+          <t>553,019</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>児童手当240,000円、旧簡易水道事業起債利子償還313,019円</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち繰出基準外</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>166,434,074</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>職員給与費28,566,469円、施設等保険料9,077,628円、江島海底送水管応急修繕等128,789,977円</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>基準外を除いた経常収益</t>
+        </is>
+      </c>
+      <c r="B44" s="66" t="inlineStr">
+        <is>
+          <t>488,905,033</t>
+        </is>
+      </c>
+      <c r="C44" s="66" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>経常費用</t>
+        </is>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>674,928,751</t>
+        </is>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>経常収支比率（実質）</t>
+        </is>
+      </c>
+      <c r="B46" s="66" t="inlineStr">
+        <is>
+          <t>72.44％</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>★公表ベース97.10％に対し24.66pt低い。R6実質（88.12％−基準外分）よりも悪化している可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="54" t="inlineStr">
+        <is>
+          <t>■　算式の検証　－　公表値（令和５年度決算）で再現を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="55" t="inlineStr">
+        <is>
+          <t>指　標</t>
+        </is>
+      </c>
+      <c r="B49" s="55" t="inlineStr">
+        <is>
+          <t>算　式</t>
+        </is>
+      </c>
+      <c r="C49" s="55" t="inlineStr">
+        <is>
+          <t>R5での検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>料金回収率</t>
+        </is>
+      </c>
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>給水収益 ÷（経常費用 − 長期前受金戻入益）× 100</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>120,553,459 ÷ 228,019,458 ＝ 52.87％　→　公表値52.87％と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="40" t="inlineStr">
+        <is>
+          <t>給水原価</t>
+        </is>
+      </c>
+      <c r="B51" s="40" t="inlineStr">
+        <is>
+          <t>（経常費用 − 長期前受金戻入益）÷ 年間総有収水量</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>228,019,458 ÷ 1,042,900㎥ ＝ 218.64円　→　公表値218.64円と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>累積欠損金比率</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>当年度未処理欠損金 ÷（営業収益 − 受託工事収益）× 100</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="inlineStr">
+        <is>
+          <t>R5末欠損金 約1,084,965千円 ÷ 120,750千円 ＝ 898.5％　→　公表値898.52％と整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="40" t="inlineStr">
+        <is>
+          <t>有収率</t>
+        </is>
+      </c>
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>年間総有収水量 ÷ 年間総配水量 × 100</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>R7：1,024,576㎥ ÷ 1,391,383㎥ ＝ 73.64％　→　決算書掲載値と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>経費回収率（下水道）</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>使用料単価 ÷ 汚水処理原価 × 100</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>R7：189.99円 ÷ 248.74円 ＝ 76.38％　→　決算書掲載値と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="54" t="inlineStr">
+        <is>
+          <t>■　経営戦略（案）の記載と指標実績との齟齬　－　要修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="55" t="inlineStr">
+        <is>
+          <t>箇　所</t>
+        </is>
+      </c>
+      <c r="B57" s="55" t="inlineStr">
+        <is>
+          <t>経営戦略（案）の記載</t>
+        </is>
+      </c>
+      <c r="C57" s="55" t="inlineStr">
+        <is>
+          <t>指標実績（R7）</t>
+        </is>
+      </c>
+      <c r="D57" s="55" t="inlineStr">
+        <is>
+          <t>対　応</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>水道 4-4 (1) 投資の目標</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>「管路経年化率が全国水準（51.38％）を超えないように」</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>51.38％は【有形固定資産減価償却率】の類似団体平均（R5）。管路経年化率の全国平均は25.37％、類似団体平均は21.60％</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>★指標名・平均の種類とも誤り。目標値の設定根拠から見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="40" t="inlineStr">
+        <is>
+          <t>水道 3-8 (2) 給水原価</t>
+        </is>
+      </c>
+      <c r="B59" s="40" t="inlineStr">
+        <is>
+          <t>「おおむね類似団体の平均値よりも低い値となり、事業運営は効率的であると言える」</t>
+        </is>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>R7：332.50円 ＞ 類似団体平均230.21円</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>★評価が逆転。記述の全面見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>水道 3-8 (3) 有収率</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="inlineStr">
+        <is>
+          <t>「平均87％で推移しており、他の類似団体の平均値よりも高く、効率的な施設運営」</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
+          <t>R7：73.64％ ＜ 類似団体平均76.64％</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>★評価が逆転。捨水・応急給水という原因の明示が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>水道 3-8 (4) 流動比率</t>
+        </is>
+      </c>
+      <c r="B61" s="40" t="inlineStr">
+        <is>
+          <t>「常に100％を上回り短期的な財務健全性は良好」</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>R7：141.21％（R5 188.42％から低下）。類似団体平均311.12％の半分以下</t>
+        </is>
+      </c>
+      <c r="D61" s="40" t="inlineStr">
+        <is>
+          <t>低下傾向と現金預金の減少を追記</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>水道 3-8 (5) 企業債残高対給水収益比率</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="inlineStr">
+        <is>
+          <t>「令和５年度で600％代まで上昇」</t>
+        </is>
+      </c>
+      <c r="C62" s="64" t="inlineStr">
+        <is>
+          <t>R7：915.92％</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>R7まで延伸。900％台への到達を明記</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="40" t="inlineStr">
+        <is>
+          <t>水道 3-8 経営分析　全体</t>
+        </is>
+      </c>
+      <c r="B63" s="40" t="inlineStr">
+        <is>
+          <t>①経常収支比率 ②給水原価 ③有収率 ④流動比率 ⑤企業債残高対給水収益比率 ⑥料金回収率 ⑦有形固定資産減価償却率・管路経年化率　の8項目</t>
+        </is>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>【累積欠損金比率】【施設利用率】【管路更新率】の3指標が未記載</t>
+        </is>
+      </c>
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>★特に累積欠損金比率（R7 2,286.55％、類似団体平均27.85％）は最も深刻。追加が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>下水道 Ⅱ-2 (3) 経常収支比率</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>「令和５年度78.86％」（経営比較分析表ベース）</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>決算書はR7 69.96％（算式が異なる）</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>経営戦略では経営比較分析表の算式に統一し、出典を明記</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="54" t="inlineStr">
+        <is>
+          <t>■　試算シート（20251209版）の令和７年度推計と決算実績との乖離</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="55" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="B67" s="55" t="inlineStr">
+        <is>
+          <t>試算シート R7</t>
+        </is>
+      </c>
+      <c r="C67" s="55" t="inlineStr">
+        <is>
+          <t>決算実績 R7</t>
+        </is>
+      </c>
+      <c r="D67" s="55" t="inlineStr">
+        <is>
+          <t>乖　離</t>
+        </is>
+      </c>
+      <c r="E67" s="55" t="inlineStr">
+        <is>
+          <t>評　価</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="B68" s="64" t="inlineStr">
+        <is>
+          <t>393,178,325</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="inlineStr">
+        <is>
+          <t>393,745,802</t>
+        </is>
+      </c>
+      <c r="D68" s="64" t="inlineStr">
+        <is>
+          <t>+567,477</t>
+        </is>
+      </c>
+      <c r="E68" s="64" t="inlineStr">
+        <is>
+          <t>○　ほぼ一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="40" t="inlineStr">
+        <is>
+          <t>企業債償還金</t>
+        </is>
+      </c>
+      <c r="B69" s="66" t="inlineStr">
+        <is>
+          <t>18,171,249</t>
+        </is>
+      </c>
+      <c r="C69" s="66" t="inlineStr">
+        <is>
+          <t>18,171,249</t>
+        </is>
+      </c>
+      <c r="D69" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E69" s="66" t="inlineStr">
+        <is>
+          <t>○　一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>当年度純損益</t>
+        </is>
+      </c>
+      <c r="B70" s="64" t="inlineStr">
+        <is>
+          <t>△49,845,508</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="inlineStr">
+        <is>
+          <t>△1,578,298,809</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>△1,528,453,301</t>
+        </is>
+      </c>
+      <c r="E70" s="34" t="inlineStr">
+        <is>
+          <t>－　差は全額が過年度修正（一過性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（一過性を除く経常損失）</t>
+        </is>
+      </c>
+      <c r="B71" s="66" t="inlineStr">
+        <is>
+          <t>△49,845,508</t>
+        </is>
+      </c>
+      <c r="C71" s="66" t="inlineStr">
+        <is>
+          <t>△19,589,644</t>
+        </is>
+      </c>
+      <c r="D71" s="66" t="inlineStr">
+        <is>
+          <t>+30,255,864</t>
+        </is>
+      </c>
+      <c r="E71" s="40" t="inlineStr">
+        <is>
+          <t>△　実績が良いが基準外繰入166,434千円による</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>資金残高（年度末）</t>
+        </is>
+      </c>
+      <c r="B72" s="64" t="inlineStr">
+        <is>
+          <t>120,919,384</t>
+        </is>
+      </c>
+      <c r="C72" s="64" t="inlineStr">
+        <is>
+          <t>50,295,933</t>
+        </is>
+      </c>
+      <c r="D72" s="64" t="inlineStr">
+        <is>
+          <t>△70,623,451</t>
+        </is>
+      </c>
+      <c r="E72" s="64" t="inlineStr">
+        <is>
+          <t>×　★起点が7千万円下振れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="40" t="inlineStr">
+        <is>
+          <t>企業債残高（年度末）</t>
+        </is>
+      </c>
+      <c r="B73" s="66" t="inlineStr">
+        <is>
+          <t>585,276,765</t>
+        </is>
+      </c>
+      <c r="C73" s="66" t="inlineStr">
+        <is>
+          <t>1,094,345,662</t>
+        </is>
+      </c>
+      <c r="D73" s="66" t="inlineStr">
+        <is>
+          <t>+509,068,897</t>
+        </is>
+      </c>
+      <c r="E73" s="40" t="inlineStr">
+        <is>
+          <t>×　★約5億円の差。元利償還表の網羅性を要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="54" t="inlineStr">
+        <is>
+          <t>■　更新にあたって差し替えが必要な前提条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="55" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B76" s="55" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="C76" s="55" t="inlineStr">
+        <is>
+          <t>現行案</t>
+        </is>
+      </c>
+      <c r="D76" s="55" t="inlineStr">
+        <is>
+          <t>差替後</t>
+        </is>
+      </c>
+      <c r="E76" s="55" t="inlineStr">
+        <is>
+          <t>影　響</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B77" s="64" t="inlineStr">
+        <is>
+          <t>企業債残高の起点</t>
+        </is>
+      </c>
+      <c r="C77" s="64" t="inlineStr">
+        <is>
+          <t>R7末 585,277千円</t>
+        </is>
+      </c>
+      <c r="D77" s="34" t="inlineStr">
+        <is>
+          <t>R7末 1,094,346千円</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="inlineStr">
+        <is>
+          <t>④企業債残高対給水収益比率が915.92％から出発。支払利息も再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B78" s="66" t="inlineStr">
+        <is>
+          <t>支払利息の利率</t>
+        </is>
+      </c>
+      <c r="C78" s="40" t="inlineStr">
+        <is>
+          <t>企業債残高 × 加重平均2.1％（一律）</t>
+        </is>
+      </c>
+      <c r="D78" s="40" t="inlineStr">
+        <is>
+          <t>既往債は実効約1.05％、新規債は借入時利率（R7実績の加重平均2.58％）</t>
+        </is>
+      </c>
+      <c r="E78" s="40" t="inlineStr">
+        <is>
+          <t>★一律2.1％のまま残高を実績に差し替えると支払利息が約2.2倍に膨らむ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B79" s="64" t="inlineStr">
+        <is>
+          <t>費用推計の基準期間</t>
+        </is>
+      </c>
+      <c r="C79" s="64" t="inlineStr">
+        <is>
+          <t>R1〜R5の5か年平均</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="inlineStr">
+        <is>
+          <t>R3〜R7の5か年平均（特別損益を除く）</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="inlineStr">
+        <is>
+          <t>経常費用の平均が約540百万円→約612百万円（+13.3％）に上昇</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B80" s="66" t="inlineStr">
+        <is>
+          <t>資金残高の起点</t>
+        </is>
+      </c>
+      <c r="C80" s="66" t="inlineStr">
+        <is>
+          <t>R7末 120,919千円</t>
+        </is>
+      </c>
+      <c r="D80" s="66" t="inlineStr">
+        <is>
+          <t>R7末 50,296千円</t>
+        </is>
+      </c>
+      <c r="E80" s="40" t="inlineStr">
+        <is>
+          <t>★計画期間中の資金ショート時期が大幅に前倒しとなる可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B81" s="64" t="inlineStr">
+        <is>
+          <t>給水収益の起点</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
+        <is>
+          <t>R8推計 121,539千円</t>
+        </is>
+      </c>
+      <c r="D81" s="34" t="inlineStr">
+        <is>
+          <t>R7実績 119,481千円からの再推計</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>年間約2,000〜3,500千円の下方修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B82" s="66" t="inlineStr">
+        <is>
+          <t>有収水量・有収率</t>
+        </is>
+      </c>
+      <c r="C82" s="66" t="inlineStr">
+        <is>
+          <t>有収率は平均87％前提</t>
+        </is>
+      </c>
+      <c r="D82" s="40" t="inlineStr">
+        <is>
+          <t>R7実績73.64％。捨水・応急給水の解消時期を設定</t>
+        </is>
+      </c>
+      <c r="E82" s="40" t="inlineStr">
+        <is>
+          <t>★鷲神浄水場高度処理施設の完成時期、江島海底送水管の本復旧時期の確認が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B83" s="64" t="inlineStr">
+        <is>
+          <t>料金改定率</t>
+        </is>
+      </c>
+      <c r="C83" s="34" t="inlineStr">
+        <is>
+          <t>基本料金×1.5／従量料金×1.0</t>
+        </is>
+      </c>
+      <c r="D83" s="34" t="inlineStr">
+        <is>
+          <t>料金回収率35.07％を起点に再設定</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>現行案の改定率では料金回収率100％に到達しない可能性が高い</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A75:M75"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
+++ b/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
@@ -9438,7 +9438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9466,7 +9466,7 @@
     <row r="2">
       <c r="A2" s="53" t="inlineStr">
         <is>
-          <t>R1〜R5＝公表済の経営比較分析表（令和５年度決算）の値。R6・R7＝決算書および決算書掲載の経営指標から算定した値（決算統計提出前のため概算）。算式は公表値で検証済（R5の料金回収率52.87％・給水原価218.64円を再現）。</t>
+          <t>R1〜R5＝公表済の経営比較分析表（令和５年度決算）の値。R6・R7＝決算書および決算書掲載の経営指標から算定した値。算式は公表値で検証済（R5の料金回収率52.87％・給水原価218.64円を再現）。※令和６年度決算の経営比較分析表は公表済みのため、R6は公表値に差し替え可能（本シート最終節を参照）。</t>
         </is>
       </c>
     </row>
@@ -11854,8 +11854,284 @@
         </is>
       </c>
     </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="54" t="inlineStr">
+        <is>
+          <t>■　令和６年度決算の経営比較分析表は公表済み　－　R6は公表値に差し替え可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="55" t="inlineStr">
+        <is>
+          <t>公表主体</t>
+        </is>
+      </c>
+      <c r="B86" s="55" t="inlineStr">
+        <is>
+          <t>内　容</t>
+        </is>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>所　在</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>総務省</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>令和6年度決算 経営比較分析</t>
+        </is>
+      </c>
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>https://www.soumu.go.jp/main_sosiki/c-zaisei/kouei/r06keieihikakubunsekihyo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="40" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="B88" s="40" t="inlineStr">
+        <is>
+          <t>令和6年度決算経営比較分析表（団体別）　※女川町のExcelあり</t>
+        </is>
+      </c>
+      <c r="C88" s="40" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyagi.jp/soshiki/sichouson/r6kessan-keieihikakubunsekihyo-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="34" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="B89" s="34" t="inlineStr">
+        <is>
+          <t>令和6年度決算経営比較分析表（事業別）</t>
+        </is>
+      </c>
+      <c r="C89" s="34" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyagi.jp/soshiki/sichouson/r6kessan-keieihikakubunsekihyo-2.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="40" t="inlineStr">
+        <is>
+          <t>総務省</t>
+        </is>
+      </c>
+      <c r="B90" s="66" t="inlineStr">
+        <is>
+          <t>令和6年度地方公営企業年鑑</t>
+        </is>
+      </c>
+      <c r="C90" s="40" t="inlineStr">
+        <is>
+          <t>https://www.soumu.go.jp/main_sosiki/c-zaisei/kouei_R06/index_so.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="34" t="inlineStr">
+        <is>
+          <t>女川町</t>
+        </is>
+      </c>
+      <c r="B91" s="34" t="inlineStr">
+        <is>
+          <t>経営比較分析表は当該市町村でも公表されるため、町でも令和６年度分を公表済みのはず</t>
+        </is>
+      </c>
+      <c r="C91" s="34" t="inlineStr">
+        <is>
+          <t>町ホームページ（財政状況）または上下水道課の手元資料をご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>現　状</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>令和６年度分を入手した後</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="34" t="inlineStr">
+        <is>
+          <t>水道 R6の指標</t>
+        </is>
+      </c>
+      <c r="B94" s="34" t="inlineStr">
+        <is>
+          <t>5指標のみ判明（決算書掲載分）</t>
+        </is>
+      </c>
+      <c r="C94" s="34" t="inlineStr">
+        <is>
+          <t>★11指標すべてが公表値で確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="40" t="inlineStr">
+        <is>
+          <t>公共下水道 R6の指標</t>
+        </is>
+      </c>
+      <c r="B95" s="66" t="inlineStr">
+        <is>
+          <t>4指標のみ判明</t>
+        </is>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>★11指標すべてが公表値で確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="34" t="inlineStr">
+        <is>
+          <t>類似団体平均・全国平均</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>R5ベース（本シートの比較欄）</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="inlineStr">
+        <is>
+          <t>★R6ベースに更新し比較欄を全面差替</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="40" t="inlineStr">
+        <is>
+          <t>管路経年化率・管路更新率の食い違い</t>
+        </is>
+      </c>
+      <c r="B97" s="40" t="inlineStr">
+        <is>
+          <t>R1〜R5の公表値0％と決算書15.60％が不一致</t>
+        </is>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>R6公表値でどちらの系列に沿って報告されているかが判明</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="34" t="inlineStr">
+        <is>
+          <t>R7の指標</t>
+        </is>
+      </c>
+      <c r="B98" s="64" t="inlineStr">
+        <is>
+          <t>決算書ベースの概算</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="inlineStr">
+        <is>
+          <t>概算のまま（令和７年度分の公表は令和９年３月頃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="40" t="inlineStr">
+        <is>
+          <t>経営戦略（案）3-8の記述</t>
+        </is>
+      </c>
+      <c r="B99" s="40" t="inlineStr">
+        <is>
+          <t>「令和５年度度決算に係る経営比較分析表を公表しています」</t>
+        </is>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>★令和６年度分に差替（資料４〜11のグラフも同時に差替。誤字「年度度」も修正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="A101" s="55" t="inlineStr">
+        <is>
+          <t>確認事項</t>
+        </is>
+      </c>
+      <c r="B101" s="55" t="inlineStr">
+        <is>
+          <t>内　容</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="46" customHeight="1">
+      <c r="A102" s="34" t="inlineStr">
+        <is>
+          <t>既提供資料は令和６年度分でした</t>
+        </is>
+      </c>
+      <c r="B102" s="34" t="inlineStr">
+        <is>
+          <t>「001066437-団体累計別平均_水道.xlsx」「001066588-類型別平均_下水道.xlsx」は令和６年度の類型別平均です。決算審査意見書（案）の比較値と完全に一致することを確認しました</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="46" customHeight="1">
+      <c r="A103" s="40" t="inlineStr">
+        <is>
+          <t>水道の有収率の比較値</t>
+        </is>
+      </c>
+      <c r="B103" s="40" t="inlineStr">
+        <is>
+          <t>意見書の表「81.47％」が正（給水人口5千人～1万人区分）。本文の「83.47％」は誤りで、差は7.83ポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="46" customHeight="1">
+      <c r="A104" s="34" t="inlineStr">
+        <is>
+          <t>★下水道の比較に用いる類型区分</t>
+        </is>
+      </c>
+      <c r="B104" s="34" t="inlineStr">
+        <is>
+          <t>意見書はDd2（汚水処理原価263.79円）で比較。一方、経営比較分析表・下水道経営戦略（案）では女川町はCd2（同203.06円）。「下水道事業経営指標」（A〜Eの5区分）と「経営比較分析表」（A〜Cの3区分）で刻みが異なるため要確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A66:M66"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A75:M75"/>
@@ -11866,6 +12142,7 @@
     <mergeCell ref="A56:M56"/>
     <mergeCell ref="A39:M39"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A85:M85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
+++ b/onagawa/output/女川町_上下水道事業_支援業務工程表.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_R7決算サマリと差異" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_会計システム見直し" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_経営比較分析表_指標検証" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_中間報告_R8年9月末" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -981,7 +982,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>作成日：令和８年８月　／　対象：上水道事業・公共下水道事業・浄化槽事業</t>
+          <t>業務名：令和８年度 上下水道経営指標評価書作成等業務委託（女川町）　／　★中間報告期限：令和８年９月30日　／　対象：上水道事業・公共下水道事業・浄化槽事業</t>
         </is>
       </c>
     </row>
@@ -1015,268 +1016,339 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>１</t>
+          <t>★</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>経営戦略の更新・再評価</t>
+          <t>中間報告（令和８年９月末）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和７年度決算を反映した経営戦略（案）の数値更新と再評価。水道・下水道の２事業。</t>
+          <t>令和８年度 上下水道経営指標評価書作成等業務委託の中間報告。仕様書が求める3パターンシミュレーションの再計算と報告書作成。</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>令和８年８月〜令和９年３月</t>
+          <t>令和８年８月〜９月　※期限 9/30</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>01_経営戦略の更新</t>
+          <t>07_中間報告_R8年9月末</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>１(2)</t>
+          <t>１</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>浄化槽事業　経営戦略の策定</t>
+          <t>経営戦略の更新・再評価</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>下水道事業会計の報告セグメントである浄化槽事業について、公営企業版の経営戦略を新規策定。</t>
+          <t>令和７年度決算を反映した経営戦略（案）の数値更新と再評価。水道・下水道の２事業。</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>令和８年８月〜令和10年３月</t>
+          <t>令和８年８月〜令和９年３月</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>02_浄化槽_経営戦略策定</t>
+          <t>01_経営戦略の更新</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>２</t>
+          <t>１(2)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>財務・経営指標分析による課題抽出と改善案作成</t>
+          <t>浄化槽事業　経営戦略の策定</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>経営指標の算定・類似団体比較から課題を抽出し、改善案と料金改定提案を作成。</t>
+          <t>下水道事業会計の報告セグメントである浄化槽事業について、公営企業版の経営戦略を新規策定。</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>令和８年８月〜令和９年４月</t>
+          <t>令和８年８月〜令和10年３月</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>03_財務経営指標分析</t>
+          <t>02_浄化槽_経営戦略策定</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>－</t>
+          <t>２</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>令和７年度決算サマリと差異</t>
+          <t>財務・経営指標分析による課題抽出と改善案作成</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>決算の主要数値と、経営戦略（案）の記載との差異一覧。上記１・２の共通インプット。</t>
+          <t>経営指標の算定・類似団体比較から課題を抽出し、改善案と料金改定提案を作成。</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>－</t>
+          <t>令和８年８月〜令和９年４月</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>04_R7決算サマリと差異</t>
+          <t>03_財務経営指標分析</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>令和７年度決算サマリと差異</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>決算の主要数値と、経営戦略（案）の記載との差異一覧。上記１・２の共通インプット。</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>04_R7決算サマリと差異</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
           <t>３</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>会計システムの見直し</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>決算審査で顕在化した課題の整理、ビズアップの提供範囲、予算獲得に向けた考え方。</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>令和８年８月〜（令和９年度当初予算要求）</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>05_会計システム見直し</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>■　直近で決めていただきたい事項</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="inlineStr"/>
-      <c r="B12" s="11" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>理　由</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>期　限</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>料金改定の施行目標時期（水道）</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>審議会・条例改正・システム改修・住民周知から逆算するため。決まればシート03の後続工程を確定できます。</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>令和８年10月まで</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>★</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>浄化槽事業の経営戦略：単独策定か、下水道経営戦略への統合か</t>
+          <t>税抜／税込の統一ルール、および料金回収率・給水原価の年度と算式の統一</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>統合方式なら期間・費用とも圧縮できます。予算要求の内容が変わるため先に決定が必要です。</t>
+          <t>引継ぎメモの数値と決算書に5点の食い違い。成果物全体の数値に影響します。詳細は『06_引継ぎメモの突合と作業履歴.md』</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>令和８年10月上旬</t>
+          <t>令和８年８月中旬</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>★</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>浄化槽事業の実施年度（パターンＡ：令和８年度／パターンＢ：令和９年度）</t>
+          <t>claude.ai セッションの成果物8ファイルと業務仕様書のご提供</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>令和８年度内に行う場合は補正予算等の財源措置が必要です。</t>
+          <t>突合の完了と、中間報告書の体裁確定に必要です。</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>令和８年９月中</t>
+          <t>至急</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>令和９年度当初予算の要求締切</t>
+          <t>料金改定の施行目標時期（水道）</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>会計システム・浄化槽経営戦略とも、この日程から逆算します。</t>
+          <t>審議会・条例改正・システム改修・住民周知から逆算するため。決まればシート03の後続工程を確定できます。</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>至急</t>
+          <t>令和８年10月まで</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>浄化槽事業の経営戦略：単独策定か、下水道経営戦略への統合か</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>統合方式なら期間・費用とも圧縮できます。予算要求の内容が変わるため先に決定が必要です。</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>令和８年10月上旬</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>浄化槽事業の実施年度（パターンＡ：令和８年度／パターンＢ：令和９年度）</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>令和８年度内に行う場合は補正予算等の財源措置が必要です。</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>令和８年９月中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>令和９年度当初予算の要求締切</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>会計システム・浄化槽経営戦略とも、この日程から逆算します。</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>至急</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>経営戦略（案）に未計上の投資事業の事業費・年割</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>鷲神浄水場高度処理施設、江島海底送水管本復旧。収支計画に直結します。</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>令和８年10月まで</t>
         </is>
@@ -1284,7 +1356,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12146,4 +12218,1547 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="2.6" customWidth="1" min="5" max="5"/>
+    <col width="2.6" customWidth="1" min="6" max="6"/>
+    <col width="2.6" customWidth="1" min="7" max="7"/>
+    <col width="2.6" customWidth="1" min="8" max="8"/>
+    <col width="2.6" customWidth="1" min="9" max="9"/>
+    <col width="2.6" customWidth="1" min="10" max="10"/>
+    <col width="2.6" customWidth="1" min="11" max="11"/>
+    <col width="2.6" customWidth="1" min="12" max="12"/>
+    <col width="2.6" customWidth="1" min="13" max="13"/>
+    <col width="2.6" customWidth="1" min="14" max="14"/>
+    <col width="2.6" customWidth="1" min="15" max="15"/>
+    <col width="2.6" customWidth="1" min="16" max="16"/>
+    <col width="2.6" customWidth="1" min="17" max="17"/>
+    <col width="2.6" customWidth="1" min="18" max="18"/>
+    <col width="2.6" customWidth="1" min="19" max="19"/>
+    <col width="2.6" customWidth="1" min="20" max="20"/>
+    <col width="2.6" customWidth="1" min="21" max="21"/>
+    <col width="2.6" customWidth="1" min="22" max="22"/>
+    <col width="2.6" customWidth="1" min="23" max="23"/>
+    <col width="2.6" customWidth="1" min="24" max="24"/>
+    <col width="2.6" customWidth="1" min="25" max="25"/>
+    <col width="2.6" customWidth="1" min="26" max="26"/>
+    <col width="2.6" customWidth="1" min="27" max="27"/>
+    <col width="2.6" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>７　中間報告（令和８年９月末）に向けた工程　－　令和８年度 上下水道経営指標評価書作成等業務委託</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>業務名：令和８年度 上下水道経営指標評価書作成等業務委託（女川町）　／　中間報告期限：令和８年９月30日</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>ビズアップ主担当</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>町（上下水道課）主担当</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>準備・調整・待機</t>
+        </is>
+      </c>
+      <c r="S3" s="21" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>任意／条件付き工程</t>
+        </is>
+      </c>
+      <c r="Y3" s="22" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Z3" s="18" t="inlineStr">
+        <is>
+          <t>マイルストーン（議会・審議会等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>区　分</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>工　程</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>主担当</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>令和８年度</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="26" t="n"/>
+      <c r="AC4" s="23" t="inlineStr">
+        <is>
+          <t>備　考／成果物</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="26" t="n"/>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="26" t="n"/>
+      <c r="N5" s="28" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="26" t="n"/>
+      <c r="Q5" s="28" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="26" t="n"/>
+      <c r="T5" s="28" t="inlineStr">
+        <is>
+          <t>R9.1</t>
+        </is>
+      </c>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="26" t="n"/>
+      <c r="W5" s="28" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="26" t="n"/>
+      <c r="Z5" s="28" t="inlineStr">
+        <is>
+          <t>R9.3</t>
+        </is>
+      </c>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="26" t="n"/>
+      <c r="AC5" s="27" t="n"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="O6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="P6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="Q6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="R6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="S6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="T6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="U6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="V6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="W6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="X6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Y6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="Z6" s="30" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="AA6" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="AB6" s="30" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="AC6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Ⅰ　数値の突合と是正（８月上旬〜中旬）</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="32" t="n"/>
+      <c r="J7" s="32" t="n"/>
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="32" t="n"/>
+      <c r="M7" s="32" t="n"/>
+      <c r="N7" s="32" t="n"/>
+      <c r="O7" s="32" t="n"/>
+      <c r="P7" s="32" t="n"/>
+      <c r="Q7" s="32" t="n"/>
+      <c r="R7" s="32" t="n"/>
+      <c r="S7" s="32" t="n"/>
+      <c r="T7" s="32" t="n"/>
+      <c r="U7" s="32" t="n"/>
+      <c r="V7" s="32" t="n"/>
+      <c r="W7" s="32" t="n"/>
+      <c r="X7" s="32" t="n"/>
+      <c r="Y7" s="32" t="n"/>
+      <c r="Z7" s="32" t="n"/>
+      <c r="AA7" s="32" t="n"/>
+      <c r="AB7" s="32" t="n"/>
+      <c r="AC7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>突合</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>claude.ai セッションの成果物8ファイルの受領</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="37" t="n"/>
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="37" t="n"/>
+      <c r="K8" s="37" t="n"/>
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="37" t="n"/>
+      <c r="O8" s="37" t="n"/>
+      <c r="P8" s="37" t="n"/>
+      <c r="Q8" s="37" t="n"/>
+      <c r="R8" s="37" t="n"/>
+      <c r="S8" s="37" t="n"/>
+      <c r="T8" s="37" t="n"/>
+      <c r="U8" s="37" t="n"/>
+      <c r="V8" s="37" t="n"/>
+      <c r="W8" s="37" t="n"/>
+      <c r="X8" s="37" t="n"/>
+      <c r="Y8" s="37" t="n"/>
+      <c r="Z8" s="37" t="n"/>
+      <c r="AA8" s="37" t="n"/>
+      <c r="AB8" s="37" t="n"/>
+      <c r="AC8" s="38" t="inlineStr">
+        <is>
+          <t>基幹の onagawa_rate_reform_v1.xlsx、仕様書整合確認まとめ（md）を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>突合</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>業務仕様書の受領（3パターンの定義・成果物要求水準・中間報告様式）</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="41" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="41" t="n"/>
+      <c r="M9" s="41" t="n"/>
+      <c r="N9" s="41" t="n"/>
+      <c r="O9" s="41" t="n"/>
+      <c r="P9" s="41" t="n"/>
+      <c r="Q9" s="41" t="n"/>
+      <c r="R9" s="41" t="n"/>
+      <c r="S9" s="41" t="n"/>
+      <c r="T9" s="41" t="n"/>
+      <c r="U9" s="41" t="n"/>
+      <c r="V9" s="41" t="n"/>
+      <c r="W9" s="41" t="n"/>
+      <c r="X9" s="41" t="n"/>
+      <c r="Y9" s="41" t="n"/>
+      <c r="Z9" s="41" t="n"/>
+      <c r="AA9" s="41" t="n"/>
+      <c r="AB9" s="41" t="n"/>
+      <c r="AC9" s="43" t="inlineStr">
+        <is>
+          <t>★未入手。報告書の体裁を確定するために必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>税抜／税込の統一ルールの確定と全ファイルへの適用</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="37" t="n"/>
+      <c r="L10" s="37" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="37" t="n"/>
+      <c r="O10" s="37" t="n"/>
+      <c r="P10" s="37" t="n"/>
+      <c r="Q10" s="37" t="n"/>
+      <c r="R10" s="37" t="n"/>
+      <c r="S10" s="37" t="n"/>
+      <c r="T10" s="37" t="n"/>
+      <c r="U10" s="37" t="n"/>
+      <c r="V10" s="37" t="n"/>
+      <c r="W10" s="37" t="n"/>
+      <c r="X10" s="37" t="n"/>
+      <c r="Y10" s="37" t="n"/>
+      <c r="Z10" s="37" t="n"/>
+      <c r="AA10" s="37" t="n"/>
+      <c r="AB10" s="37" t="n"/>
+      <c r="AC10" s="38" t="inlineStr">
+        <is>
+          <t>★引継ぎメモの料金収入131,428,825円は税込。税抜は119,480,750円</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>料金回収率・給水原価の年度と算式の統一</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="41" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="41" t="n"/>
+      <c r="M11" s="41" t="n"/>
+      <c r="N11" s="41" t="n"/>
+      <c r="O11" s="41" t="n"/>
+      <c r="P11" s="41" t="n"/>
+      <c r="Q11" s="41" t="n"/>
+      <c r="R11" s="41" t="n"/>
+      <c r="S11" s="41" t="n"/>
+      <c r="T11" s="41" t="n"/>
+      <c r="U11" s="41" t="n"/>
+      <c r="V11" s="41" t="n"/>
+      <c r="W11" s="41" t="n"/>
+      <c r="X11" s="41" t="n"/>
+      <c r="Y11" s="41" t="n"/>
+      <c r="Z11" s="41" t="n"/>
+      <c r="AA11" s="41" t="n"/>
+      <c r="AB11" s="41" t="n"/>
+      <c r="AC11" s="43" t="inlineStr">
+        <is>
+          <t>★52.87％はR5の値。R7は35.07％。給水原価は5通りの値が併存</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Ⅱ　確定値の反映（８月中旬〜下旬）</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="32" t="n"/>
+      <c r="L12" s="32" t="n"/>
+      <c r="M12" s="32" t="n"/>
+      <c r="N12" s="32" t="n"/>
+      <c r="O12" s="32" t="n"/>
+      <c r="P12" s="32" t="n"/>
+      <c r="Q12" s="32" t="n"/>
+      <c r="R12" s="32" t="n"/>
+      <c r="S12" s="32" t="n"/>
+      <c r="T12" s="32" t="n"/>
+      <c r="U12" s="32" t="n"/>
+      <c r="V12" s="32" t="n"/>
+      <c r="W12" s="32" t="n"/>
+      <c r="X12" s="32" t="n"/>
+      <c r="Y12" s="32" t="n"/>
+      <c r="Z12" s="32" t="n"/>
+      <c r="AA12" s="32" t="n"/>
+      <c r="AB12" s="32" t="n"/>
+      <c r="AC12" s="32" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>確定値</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>R7決算確定値の反映（総括原価・住民議会用シート）</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="37" t="n"/>
+      <c r="N13" s="37" t="n"/>
+      <c r="O13" s="37" t="n"/>
+      <c r="P13" s="37" t="n"/>
+      <c r="Q13" s="37" t="n"/>
+      <c r="R13" s="37" t="n"/>
+      <c r="S13" s="37" t="n"/>
+      <c r="T13" s="37" t="n"/>
+      <c r="U13" s="37" t="n"/>
+      <c r="V13" s="37" t="n"/>
+      <c r="W13" s="37" t="n"/>
+      <c r="X13" s="37" t="n"/>
+      <c r="Y13" s="37" t="n"/>
+      <c r="Z13" s="37" t="n"/>
+      <c r="AA13" s="37" t="n"/>
+      <c r="AB13" s="37" t="n"/>
+      <c r="AC13" s="38" t="inlineStr">
+        <is>
+          <t>給水収益119,480,750円、料金回収率35.07％、給水原価332.50円</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>確定値</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>有収水量推計の見直し（R7実績1,024,576㎥を起点に再推計）</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="G14" s="42" t="n"/>
+      <c r="H14" s="42" t="n"/>
+      <c r="I14" s="41" t="n"/>
+      <c r="J14" s="41" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="41" t="n"/>
+      <c r="M14" s="41" t="n"/>
+      <c r="N14" s="41" t="n"/>
+      <c r="O14" s="41" t="n"/>
+      <c r="P14" s="41" t="n"/>
+      <c r="Q14" s="41" t="n"/>
+      <c r="R14" s="41" t="n"/>
+      <c r="S14" s="41" t="n"/>
+      <c r="T14" s="41" t="n"/>
+      <c r="U14" s="41" t="n"/>
+      <c r="V14" s="41" t="n"/>
+      <c r="W14" s="41" t="n"/>
+      <c r="X14" s="41" t="n"/>
+      <c r="Y14" s="41" t="n"/>
+      <c r="Z14" s="41" t="n"/>
+      <c r="AA14" s="41" t="n"/>
+      <c r="AB14" s="41" t="n"/>
+      <c r="AC14" s="43" t="inlineStr">
+        <is>
+          <t>★案のR8推計901千㎥は1人1日439Lベース。実績は484〜496Lで12％の乖離</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>確定値</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>対象資産（期首）の確定と資産維持費の再計算</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="37" t="n"/>
+      <c r="J15" s="37" t="n"/>
+      <c r="K15" s="37" t="n"/>
+      <c r="L15" s="37" t="n"/>
+      <c r="M15" s="37" t="n"/>
+      <c r="N15" s="37" t="n"/>
+      <c r="O15" s="37" t="n"/>
+      <c r="P15" s="37" t="n"/>
+      <c r="Q15" s="37" t="n"/>
+      <c r="R15" s="37" t="n"/>
+      <c r="S15" s="37" t="n"/>
+      <c r="T15" s="37" t="n"/>
+      <c r="U15" s="37" t="n"/>
+      <c r="V15" s="37" t="n"/>
+      <c r="W15" s="37" t="n"/>
+      <c r="X15" s="37" t="n"/>
+      <c r="Y15" s="37" t="n"/>
+      <c r="Z15" s="37" t="n"/>
+      <c r="AA15" s="37" t="n"/>
+      <c r="AB15" s="37" t="n"/>
+      <c r="AC15" s="38" t="inlineStr">
+        <is>
+          <t>R8.4.1＝令和７年度末の固定資産台帳残高。1,042,625千円の範囲の根拠確認を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>確定値</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>水産加工業19社の実使用水量データの提供</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="41" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="n"/>
+      <c r="J16" s="41" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="41" t="n"/>
+      <c r="M16" s="41" t="n"/>
+      <c r="N16" s="41" t="n"/>
+      <c r="O16" s="41" t="n"/>
+      <c r="P16" s="41" t="n"/>
+      <c r="Q16" s="41" t="n"/>
+      <c r="R16" s="41" t="n"/>
+      <c r="S16" s="41" t="n"/>
+      <c r="T16" s="41" t="n"/>
+      <c r="U16" s="41" t="n"/>
+      <c r="V16" s="41" t="n"/>
+      <c r="W16" s="41" t="n"/>
+      <c r="X16" s="41" t="n"/>
+      <c r="Y16" s="41" t="n"/>
+      <c r="Z16" s="41" t="n"/>
+      <c r="AA16" s="41" t="n"/>
+      <c r="AB16" s="41" t="n"/>
+      <c r="AC16" s="43" t="inlineStr">
+        <is>
+          <t>★06シートは推計値のまま。産業影響の試算に必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Ⅲ　3パターンの再計算と分析（８月下旬〜９月上旬）</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" s="32" t="n"/>
+      <c r="K17" s="32" t="n"/>
+      <c r="L17" s="32" t="n"/>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="32" t="n"/>
+      <c r="O17" s="32" t="n"/>
+      <c r="P17" s="32" t="n"/>
+      <c r="Q17" s="32" t="n"/>
+      <c r="R17" s="32" t="n"/>
+      <c r="S17" s="32" t="n"/>
+      <c r="T17" s="32" t="n"/>
+      <c r="U17" s="32" t="n"/>
+      <c r="V17" s="32" t="n"/>
+      <c r="W17" s="32" t="n"/>
+      <c r="X17" s="32" t="n"/>
+      <c r="Y17" s="32" t="n"/>
+      <c r="Z17" s="32" t="n"/>
+      <c r="AA17" s="32" t="n"/>
+      <c r="AB17" s="32" t="n"/>
+      <c r="AC17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>仕様書対応</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>パターン1（現行体系維持）の再計算</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="42" t="n"/>
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="37" t="n"/>
+      <c r="K18" s="37" t="n"/>
+      <c r="L18" s="37" t="n"/>
+      <c r="M18" s="37" t="n"/>
+      <c r="N18" s="37" t="n"/>
+      <c r="O18" s="37" t="n"/>
+      <c r="P18" s="37" t="n"/>
+      <c r="Q18" s="37" t="n"/>
+      <c r="R18" s="37" t="n"/>
+      <c r="S18" s="37" t="n"/>
+      <c r="T18" s="37" t="n"/>
+      <c r="U18" s="37" t="n"/>
+      <c r="V18" s="37" t="n"/>
+      <c r="W18" s="37" t="n"/>
+      <c r="X18" s="37" t="n"/>
+      <c r="Y18" s="37" t="n"/>
+      <c r="Z18" s="37" t="n"/>
+      <c r="AA18" s="37" t="n"/>
+      <c r="AB18" s="37" t="n"/>
+      <c r="AC18" s="38" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>仕様書対応</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>パターン2（赤字半減案）の再計算　※「赤字」の定義を確定値で再設定</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
+      <c r="G19" s="41" t="n"/>
+      <c r="H19" s="42" t="n"/>
+      <c r="I19" s="42" t="n"/>
+      <c r="J19" s="41" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="41" t="n"/>
+      <c r="M19" s="41" t="n"/>
+      <c r="N19" s="41" t="n"/>
+      <c r="O19" s="41" t="n"/>
+      <c r="P19" s="41" t="n"/>
+      <c r="Q19" s="41" t="n"/>
+      <c r="R19" s="41" t="n"/>
+      <c r="S19" s="41" t="n"/>
+      <c r="T19" s="41" t="n"/>
+      <c r="U19" s="41" t="n"/>
+      <c r="V19" s="41" t="n"/>
+      <c r="W19" s="41" t="n"/>
+      <c r="X19" s="41" t="n"/>
+      <c r="Y19" s="41" t="n"/>
+      <c r="Z19" s="41" t="n"/>
+      <c r="AA19" s="41" t="n"/>
+      <c r="AB19" s="41" t="n"/>
+      <c r="AC19" s="43" t="inlineStr">
+        <is>
+          <t>料金回収率35.07％／経常収支比率97.10％（実質72.44％）を起点に再設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>仕様書対応</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>パターン3（口径別料金表 3-A・3-B）の再計算</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="37" t="n"/>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="37" t="n"/>
+      <c r="K20" s="37" t="n"/>
+      <c r="L20" s="37" t="n"/>
+      <c r="M20" s="37" t="n"/>
+      <c r="N20" s="37" t="n"/>
+      <c r="O20" s="37" t="n"/>
+      <c r="P20" s="37" t="n"/>
+      <c r="Q20" s="37" t="n"/>
+      <c r="R20" s="37" t="n"/>
+      <c r="S20" s="37" t="n"/>
+      <c r="T20" s="37" t="n"/>
+      <c r="U20" s="37" t="n"/>
+      <c r="V20" s="37" t="n"/>
+      <c r="W20" s="37" t="n"/>
+      <c r="X20" s="37" t="n"/>
+      <c r="Y20" s="37" t="n"/>
+      <c r="Z20" s="37" t="n"/>
+      <c r="AA20" s="37" t="n"/>
+      <c r="AB20" s="37" t="n"/>
+      <c r="AC20" s="38" t="inlineStr">
+        <is>
+          <t>3-Bは塩竈市の生産用水料金105円/㎥（税抜）を参考モデルとする産業配慮型</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>仕様書対応</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>水産加工業への影響試算（実使用水量ベース）</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="42" t="n"/>
+      <c r="J21" s="41" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="41" t="n"/>
+      <c r="M21" s="41" t="n"/>
+      <c r="N21" s="41" t="n"/>
+      <c r="O21" s="41" t="n"/>
+      <c r="P21" s="41" t="n"/>
+      <c r="Q21" s="41" t="n"/>
+      <c r="R21" s="41" t="n"/>
+      <c r="S21" s="41" t="n"/>
+      <c r="T21" s="41" t="n"/>
+      <c r="U21" s="41" t="n"/>
+      <c r="V21" s="41" t="n"/>
+      <c r="W21" s="41" t="n"/>
+      <c r="X21" s="41" t="n"/>
+      <c r="Y21" s="41" t="n"/>
+      <c r="Z21" s="41" t="n"/>
+      <c r="AA21" s="41" t="n"/>
+      <c r="AB21" s="41" t="n"/>
+      <c r="AC21" s="43" t="inlineStr">
+        <is>
+          <t>口径別への単純移行では1,000㎥/月で＋141％の負担増との試算あり。激変緩和が論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>仕様書対応</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>財務・経営指標分析の体系化（修正前後決算を含む）</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="37" t="n"/>
+      <c r="K22" s="37" t="n"/>
+      <c r="L22" s="37" t="n"/>
+      <c r="M22" s="37" t="n"/>
+      <c r="N22" s="37" t="n"/>
+      <c r="O22" s="37" t="n"/>
+      <c r="P22" s="37" t="n"/>
+      <c r="Q22" s="37" t="n"/>
+      <c r="R22" s="37" t="n"/>
+      <c r="S22" s="37" t="n"/>
+      <c r="T22" s="37" t="n"/>
+      <c r="U22" s="37" t="n"/>
+      <c r="V22" s="37" t="n"/>
+      <c r="W22" s="37" t="n"/>
+      <c r="X22" s="37" t="n"/>
+      <c r="Y22" s="37" t="n"/>
+      <c r="Z22" s="37" t="n"/>
+      <c r="AA22" s="37" t="n"/>
+      <c r="AB22" s="37" t="n"/>
+      <c r="AC22" s="38" t="inlineStr">
+        <is>
+          <t>★シート06（経営比較分析表11指標のR7再計算）をそのまま充当可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Ⅳ　中間報告書の作成（９月中旬〜下旬）</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="32" t="n"/>
+      <c r="O23" s="32" t="n"/>
+      <c r="P23" s="32" t="n"/>
+      <c r="Q23" s="32" t="n"/>
+      <c r="R23" s="32" t="n"/>
+      <c r="S23" s="32" t="n"/>
+      <c r="T23" s="32" t="n"/>
+      <c r="U23" s="32" t="n"/>
+      <c r="V23" s="32" t="n"/>
+      <c r="W23" s="32" t="n"/>
+      <c r="X23" s="32" t="n"/>
+      <c r="Y23" s="32" t="n"/>
+      <c r="Z23" s="32" t="n"/>
+      <c r="AA23" s="32" t="n"/>
+      <c r="AB23" s="32" t="n"/>
+      <c r="AC23" s="32" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>報告書</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>住民・議会説明用シートの数値差替</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="37" t="n"/>
+      <c r="K24" s="37" t="n"/>
+      <c r="L24" s="37" t="n"/>
+      <c r="M24" s="37" t="n"/>
+      <c r="N24" s="37" t="n"/>
+      <c r="O24" s="37" t="n"/>
+      <c r="P24" s="37" t="n"/>
+      <c r="Q24" s="37" t="n"/>
+      <c r="R24" s="37" t="n"/>
+      <c r="S24" s="37" t="n"/>
+      <c r="T24" s="37" t="n"/>
+      <c r="U24" s="37" t="n"/>
+      <c r="V24" s="37" t="n"/>
+      <c r="W24" s="37" t="n"/>
+      <c r="X24" s="37" t="n"/>
+      <c r="Y24" s="37" t="n"/>
+      <c r="Z24" s="37" t="n"/>
+      <c r="AA24" s="37" t="n"/>
+      <c r="AB24" s="37" t="n"/>
+      <c r="AC24" s="38" t="inlineStr">
+        <is>
+          <t>★「現行の半分しか回収できていない」→ 実際は約3分の1（35.07％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>報告書</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>中間報告書（Word）の作成</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>ビズアップ</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="n"/>
+      <c r="F25" s="41" t="n"/>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="41" t="n"/>
+      <c r="M25" s="41" t="n"/>
+      <c r="N25" s="41" t="n"/>
+      <c r="O25" s="41" t="n"/>
+      <c r="P25" s="41" t="n"/>
+      <c r="Q25" s="41" t="n"/>
+      <c r="R25" s="41" t="n"/>
+      <c r="S25" s="41" t="n"/>
+      <c r="T25" s="41" t="n"/>
+      <c r="U25" s="41" t="n"/>
+      <c r="V25" s="41" t="n"/>
+      <c r="W25" s="41" t="n"/>
+      <c r="X25" s="41" t="n"/>
+      <c r="Y25" s="41" t="n"/>
+      <c r="Z25" s="41" t="n"/>
+      <c r="AA25" s="41" t="n"/>
+      <c r="AB25" s="41" t="n"/>
+      <c r="AC25" s="43" t="inlineStr">
+        <is>
+          <t>★成果物：中間報告書。仕様書の様式に準拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>報告書</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>庁内確認</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="37" t="n"/>
+      <c r="H26" s="37" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="37" t="n"/>
+      <c r="L26" s="37" t="n"/>
+      <c r="M26" s="37" t="n"/>
+      <c r="N26" s="37" t="n"/>
+      <c r="O26" s="37" t="n"/>
+      <c r="P26" s="37" t="n"/>
+      <c r="Q26" s="37" t="n"/>
+      <c r="R26" s="37" t="n"/>
+      <c r="S26" s="37" t="n"/>
+      <c r="T26" s="37" t="n"/>
+      <c r="U26" s="37" t="n"/>
+      <c r="V26" s="37" t="n"/>
+      <c r="W26" s="37" t="n"/>
+      <c r="X26" s="37" t="n"/>
+      <c r="Y26" s="37" t="n"/>
+      <c r="Z26" s="37" t="n"/>
+      <c r="AA26" s="37" t="n"/>
+      <c r="AB26" s="37" t="n"/>
+      <c r="AC26" s="38" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>報告書</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>中間報告書の提出・報告</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="n"/>
+      <c r="F27" s="41" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="41" t="n"/>
+      <c r="I27" s="41" t="n"/>
+      <c r="J27" s="47" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="41" t="n"/>
+      <c r="M27" s="41" t="n"/>
+      <c r="N27" s="41" t="n"/>
+      <c r="O27" s="41" t="n"/>
+      <c r="P27" s="41" t="n"/>
+      <c r="Q27" s="41" t="n"/>
+      <c r="R27" s="41" t="n"/>
+      <c r="S27" s="41" t="n"/>
+      <c r="T27" s="41" t="n"/>
+      <c r="U27" s="41" t="n"/>
+      <c r="V27" s="41" t="n"/>
+      <c r="W27" s="41" t="n"/>
+      <c r="X27" s="41" t="n"/>
+      <c r="Y27" s="41" t="n"/>
+      <c r="Z27" s="41" t="n"/>
+      <c r="AA27" s="41" t="n"/>
+      <c r="AB27" s="41" t="n"/>
+      <c r="AC27" s="43" t="inlineStr">
+        <is>
+          <t>★期限：令和８年９月30日</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>Ⅴ　中間報告後（10月以降）　※既存工程に接続</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="32" t="n"/>
+      <c r="H28" s="32" t="n"/>
+      <c r="I28" s="32" t="n"/>
+      <c r="J28" s="32" t="n"/>
+      <c r="K28" s="32" t="n"/>
+      <c r="L28" s="32" t="n"/>
+      <c r="M28" s="32" t="n"/>
+      <c r="N28" s="32" t="n"/>
+      <c r="O28" s="32" t="n"/>
+      <c r="P28" s="32" t="n"/>
+      <c r="Q28" s="32" t="n"/>
+      <c r="R28" s="32" t="n"/>
+      <c r="S28" s="32" t="n"/>
+      <c r="T28" s="32" t="n"/>
+      <c r="U28" s="32" t="n"/>
+      <c r="V28" s="32" t="n"/>
+      <c r="W28" s="32" t="n"/>
+      <c r="X28" s="32" t="n"/>
+      <c r="Y28" s="32" t="n"/>
+      <c r="Z28" s="32" t="n"/>
+      <c r="AA28" s="32" t="n"/>
+      <c r="AB28" s="32" t="n"/>
+      <c r="AC28" s="32" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>後続</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>経営戦略（案）の数値更新・確定（シート01に対応）</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="37" t="n"/>
+      <c r="H29" s="37" t="n"/>
+      <c r="I29" s="37" t="n"/>
+      <c r="J29" s="37" t="n"/>
+      <c r="K29" s="44" t="n"/>
+      <c r="L29" s="44" t="n"/>
+      <c r="M29" s="44" t="n"/>
+      <c r="N29" s="44" t="n"/>
+      <c r="O29" s="44" t="n"/>
+      <c r="P29" s="44" t="n"/>
+      <c r="Q29" s="44" t="n"/>
+      <c r="R29" s="44" t="n"/>
+      <c r="S29" s="44" t="n"/>
+      <c r="T29" s="44" t="n"/>
+      <c r="U29" s="44" t="n"/>
+      <c r="V29" s="44" t="n"/>
+      <c r="W29" s="44" t="n"/>
+      <c r="X29" s="44" t="n"/>
+      <c r="Y29" s="44" t="n"/>
+      <c r="Z29" s="44" t="n"/>
+      <c r="AA29" s="44" t="n"/>
+      <c r="AB29" s="44" t="n"/>
+      <c r="AC29" s="38" t="inlineStr">
+        <is>
+          <t>投資計画への未計上事業の追加、審議会・議会説明、公表</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>後続</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>料金改定の提案・条例改正の準備</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>両者</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="41" t="n"/>
+      <c r="G30" s="41" t="n"/>
+      <c r="H30" s="41" t="n"/>
+      <c r="I30" s="41" t="n"/>
+      <c r="J30" s="41" t="n"/>
+      <c r="K30" s="44" t="n"/>
+      <c r="L30" s="44" t="n"/>
+      <c r="M30" s="44" t="n"/>
+      <c r="N30" s="44" t="n"/>
+      <c r="O30" s="44" t="n"/>
+      <c r="P30" s="44" t="n"/>
+      <c r="Q30" s="44" t="n"/>
+      <c r="R30" s="44" t="n"/>
+      <c r="S30" s="44" t="n"/>
+      <c r="T30" s="44" t="n"/>
+      <c r="U30" s="44" t="n"/>
+      <c r="V30" s="44" t="n"/>
+      <c r="W30" s="44" t="n"/>
+      <c r="X30" s="44" t="n"/>
+      <c r="Y30" s="44" t="n"/>
+      <c r="Z30" s="44" t="n"/>
+      <c r="AA30" s="44" t="n"/>
+      <c r="AB30" s="44" t="n"/>
+      <c r="AC30" s="43" t="inlineStr">
+        <is>
+          <t>施行目標時期の決定が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>【前提・留意事項】</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 本工程は引継ぎメモ（handoff_to_claude_code.md・2026年8月3日）により判明した「令和８年度 上下水道経営指標評価書作成等業務委託」の中間報告期限（令和８年９月末）に対応するものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 残り約8週間です。Ⅰの突合・是正を先に終えないと、以降の再計算がすべてやり直しになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 引継ぎメモの数値には決算書と食い違う箇所が5点あります（税抜／税込の混在、令和５年度と令和７年度の混在）。詳細は『06_引継ぎメモの突合と作業履歴.md』を参照してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ claude.ai セッションの成果物8ファイルは本リポジトリに存在しません。突合を完了させるにはご提供が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ シート01（経営戦略の更新）・シート03（財務経営指標分析）は、本工程の後続として10月以降に接続します。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="AC4:AC6"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="A34:T34"/>
+    <mergeCell ref="E4:AB4"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A36:T36"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="A7:AC7"/>
+    <mergeCell ref="A37:T37"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A12:AC12"/>
+    <mergeCell ref="A33:T33"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A32:T32"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="A23:AC23"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="A35:T35"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="A17:AC17"/>
+    <mergeCell ref="A28:AC28"/>
+    <mergeCell ref="T3:X3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>